--- a/Outputs/Data_Quality_Report.xlsx
+++ b/Outputs/Data_Quality_Report.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mshukla110689/Part1_data_cleaning/Outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB001014-30E2-2C43-AEEA-C5C9D9F89483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C2494E-8FF7-BC48-8508-12D55034C12C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="2" xr2:uid="{37640F19-421B-1D4B-B87B-4EB3842E0435}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{37640F19-421B-1D4B-B87B-4EB3842E0435}"/>
   </bookViews>
   <sheets>
     <sheet name="Order_Status_Issue_Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Sales_Profit_Mismatch_Summary" sheetId="2" r:id="rId2"/>
     <sheet name="Final_Clean_vs_Flagged" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="31">
   <si>
     <t>FINAL CLEAN VS FLAGGED RECORD COUNT</t>
   </si>
@@ -151,6 +151,15 @@
   </si>
   <si>
     <t>Reviewed and documented</t>
+  </si>
+  <si>
+    <t>The data quality assessment identified 563 clean records (60.41%) that are ready for analysis without further intervention. An additional 143 records (15.34%) were classified as warnings and can be used after business validation, while 226 records (24.25%) violated one or more business rules and were marked as invalid. Overall, the dataset contains 932 records, with clear categorization enabling reliable downstream analysis and improved data quality governance.</t>
+  </si>
+  <si>
+    <t>The validation process detected 35 sales calculation mismatches and 39 profit calculation mismatches, which were flagged for manual review. Records with missing or invalid sales and profit values were excluded from comparison to avoid misleading results. After validation, 53 records required detailed business review, ensuring that calculation inconsistencies were identified, documented, and addressed before reporting or decision-making.</t>
+  </si>
+  <si>
+    <t>Out of 932 records, 563 (60.41%) were validated as clean and are ready for analysis. A total of 143 records (15.34%) were classified as warning records that require business review before use, while 226 records (24.25%) were identified as invalid due to business rule violations. This classification ensures that only high-quality, reliable data is used for reporting and analysis while maintaining transparency over records requiring further attention.</t>
   </si>
 </sst>
 </file>
@@ -352,9 +361,6 @@
   </cellStyleXfs>
   <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -379,13 +385,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -399,27 +429,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -429,95 +438,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="32">
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -592,30 +512,30 @@
       </border>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -637,6 +557,95 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -710,30 +719,30 @@
       </border>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -768,7 +777,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5B596E3B-6103-B74D-B8B3-F1A1FC014BA7}" name="Table7" displayName="Table7" ref="A3:C7" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30" headerRowBorderDxfId="28" tableBorderDxfId="29" totalsRowBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5B596E3B-6103-B74D-B8B3-F1A1FC014BA7}" name="Table7" displayName="Table7" ref="A3:C7" totalsRowShown="0" headerRowDxfId="31" dataDxfId="29" headerRowBorderDxfId="30" tableBorderDxfId="28" totalsRowBorderDxfId="27">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{81786763-7991-B64C-B4DD-2DCAED95A3FF}" name="Record Category" dataDxfId="26"/>
     <tableColumn id="2" xr3:uid="{80216884-4541-1F42-9F21-481E17748E3D}" name="Count" dataDxfId="25"/>
@@ -789,32 +798,32 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1D126F74-7036-344F-9B68-0C5A7CC39D98}" name="Table6" displayName="Table6" ref="A4:C10" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" headerRowBorderDxfId="4" tableBorderDxfId="5" totalsRowBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1D126F74-7036-344F-9B68-0C5A7CC39D98}" name="Table6" displayName="Table6" ref="A4:C10" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{BCFB0EFB-0C74-B64E-864F-D72481927208}" name="Metric" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{5E07E64C-BC4F-5640-ACFA-5A0EA71CC107}" name="Count" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{DB20C713-6425-B84D-B203-17583DD4C7FB}" name="Action Taken" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{BCFB0EFB-0C74-B64E-864F-D72481927208}" name="Metric" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{5E07E64C-BC4F-5640-ACFA-5A0EA71CC107}" name="Count" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{DB20C713-6425-B84D-B203-17583DD4C7FB}" name="Action Taken" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FDB6F7F5-F8CD-3C4C-A5FA-141CDD1858A4}" name="Table74" displayName="Table74" ref="A3:C7" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18" headerRowBorderDxfId="16" tableBorderDxfId="17" totalsRowBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FDB6F7F5-F8CD-3C4C-A5FA-141CDD1858A4}" name="Table74" displayName="Table74" ref="A3:C7" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{5F74F856-6678-C042-A719-1F1C238A769C}" name="Record Category" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{1CE71BAA-BA5E-494E-910D-9C3A5958AD39}" name="Count" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{B742BC7B-55AE-CD43-A655-0ECE2884F30C}" name="Interpretation" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{5F74F856-6678-C042-A719-1F1C238A769C}" name="Record Category" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{1CE71BAA-BA5E-494E-910D-9C3A5958AD39}" name="Count" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{B742BC7B-55AE-CD43-A655-0ECE2884F30C}" name="Interpretation" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{643B8086-4572-4E48-BF73-009353F8E273}" name="Table95" displayName="Table95" ref="A11:B14" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{643B8086-4572-4E48-BF73-009353F8E273}" name="Table95" displayName="Table95" ref="A11:B14" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3C2F645E-B260-4543-828C-B3B47036DDA0}" name="Record Category" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{DF4C9C36-7A83-1841-979F-27D609D0307D}" name="Percentage" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{3C2F645E-B260-4543-828C-B3B47036DDA0}" name="Record Category" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{DF4C9C36-7A83-1841-979F-27D609D0307D}" name="Percentage" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1126,40 +1135,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>563</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>143</v>
       </c>
       <c r="C5" t="s">
@@ -1167,104 +1176,106 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>226</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>932</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="10"/>
+      <c r="B10" s="19"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="10">
         <f>B4/B7</f>
         <v>0.60407725321888417</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="10">
         <f>B5/B7</f>
         <v>0.15343347639484978</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="10">
         <f>B6/B7</f>
         <v>0.24248927038626608</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
     </row>
     <row r="18" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
+      <c r="A18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1291,115 +1302,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="13" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>35</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="14">
         <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>39</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="14">
         <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>195</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="14">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>195</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="14">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="7"/>
-      <c r="E9" s="20"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="6"/>
+      <c r="E9" s="14"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="22">
+      <c r="B10" s="16">
         <v>53</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="14">
         <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
     </row>
     <row r="14" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="24"/>
+      <c r="A14" s="24" t="s">
+        <v>29</v>
+      </c>
       <c r="B14" s="24"/>
       <c r="C14" s="24"/>
     </row>
@@ -1452,40 +1465,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>563</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>143</v>
       </c>
       <c r="C5" t="s">
@@ -1493,104 +1506,106 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>226</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>932</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="10"/>
+      <c r="B10" s="19"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="10">
         <f>B4/B7</f>
         <v>0.60407725321888417</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="10">
         <f>B5/B7</f>
         <v>0.15343347639484978</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="10">
         <f>B6/B7</f>
         <v>0.24248927038626608</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
     </row>
     <row r="18" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
+      <c r="A18" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="4">
